--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2375-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2375-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{177A219B-4201-4ACF-BD63-AEE8A6B361B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{80676B20-A1B7-43A2-A508-9DCB5A183928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{FF939F41-5F30-4B9F-A0AF-853754248C73}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{91C39278-B96F-4965-8B7E-5D162C4D627D}"/>
   </bookViews>
   <sheets>
     <sheet name="2375-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1451,23 +1451,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB737091-3EED-4EDF-8B16-615CE6DE90A9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FE22B8E-F20E-493A-AD53-A9B028255B61}">
   <dimension ref="A1:R47"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="7.5" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="7" width="10" customWidth="1"/>
+    <col min="8" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1495,7 +1495,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1525,7 +1525,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1571,7 +1571,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1621,7 +1621,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1731,7 +1731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1897,7 +1897,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>2.39</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="37">
         <v>2022</v>
       </c>
@@ -2395,7 +2395,7 @@
         <v>3.56</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="39">
         <v>2021</v>
       </c>
@@ -2449,7 +2449,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="37">
         <v>2020</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="39">
         <v>2019</v>
       </c>
@@ -2557,7 +2557,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="37">
         <v>2018</v>
       </c>
@@ -2611,7 +2611,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2017</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="37">
         <v>2016</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="39">
         <v>2015</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="37">
         <v>2014</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="39">
         <v>2013</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="37">
         <v>2012</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="39">
         <v>2011</v>
       </c>
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="37">
         <v>2010</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="39">
         <v>2009</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="37">
         <v>2008</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="39">
         <v>2007</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="37">
         <v>2006</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="39">
         <v>2004</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>5.69</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="37">
         <v>2003</v>
       </c>
@@ -3367,7 +3367,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="39">
         <v>2002</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="37">
         <v>2001</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="39">
         <v>2000</v>
       </c>
@@ -3529,7 +3529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>1999</v>
       </c>
@@ -3583,7 +3583,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="39">
         <v>1998</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>3.7</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="37">
         <v>1997</v>
       </c>
@@ -3691,7 +3691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="39">
         <v>1996</v>
       </c>
@@ -3745,7 +3745,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="37">
         <v>1995</v>
       </c>
@@ -3799,7 +3799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="39">
         <v>1994</v>
       </c>
@@ -3853,7 +3853,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="37">
         <v>1993</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="39" t="s">
         <v>36</v>
       </c>
